--- a/main/StructureDefinition-Person.xlsx
+++ b/main/StructureDefinition-Person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-05</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/main/StructureDefinition-Person.xlsx
+++ b/main/StructureDefinition-Person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -1054,7 +1054,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>AC</t>
@@ -1064,10 +1064,6 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Person.name.prefix.value</t>
@@ -6584,7 +6580,7 @@
         <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>113</v>
@@ -6627,7 +6623,7 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>99</v>
@@ -6693,7 +6689,7 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>20</v>
@@ -7020,7 +7016,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>96</v>
@@ -7037,10 +7033,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7066,10 +7062,10 @@
         <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7093,34 +7089,34 @@
         <v>20</v>
       </c>
       <c r="W44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -7146,10 +7142,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7175,10 +7171,10 @@
         <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7229,7 +7225,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7244,21 +7240,21 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7284,14 +7280,14 @@
         <v>246</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7340,7 +7336,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7355,21 +7351,21 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7392,19 +7388,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7441,7 +7437,7 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7451,7 +7447,7 @@
         <v>111</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -7466,24 +7462,24 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7505,19 +7501,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7566,7 +7562,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7581,21 +7577,21 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7701,10 +7697,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7812,10 +7808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7841,10 +7837,10 @@
         <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7856,7 +7852,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -7874,57 +7870,57 @@
         <v>213</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI51" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7950,16 +7946,16 @@
         <v>98</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8008,7 +8004,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8023,21 +8019,21 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8063,16 +8059,16 @@
         <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8100,28 +8096,28 @@
         <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -8142,15 +8138,15 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8173,16 +8169,16 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8232,7 +8228,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8258,10 +8254,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8287,10 +8283,10 @@
         <v>246</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8341,7 +8337,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -8356,7 +8352,7 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8367,13 +8363,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8395,19 +8391,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8456,7 +8452,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8471,21 +8467,21 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8591,10 +8587,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8702,10 +8698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8731,10 +8727,10 @@
         <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8746,7 +8742,7 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>20</v>
@@ -8764,57 +8760,57 @@
         <v>213</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="Z59" t="s" s="2">
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
+      <c r="AG59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8840,16 +8836,16 @@
         <v>98</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8898,7 +8894,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8913,21 +8909,21 @@
         <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8953,16 +8949,16 @@
         <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -8990,28 +8986,28 @@
         <v>213</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z61" t="s" s="2">
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9032,15 +9028,15 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9063,16 +9059,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9122,7 +9118,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9148,10 +9144,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9177,10 +9173,10 @@
         <v>246</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9231,7 +9227,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9246,7 +9242,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9257,10 +9253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9286,16 +9282,16 @@
         <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9323,11 +9319,11 @@
         <v>213</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9344,7 +9340,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9359,21 +9355,21 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9396,19 +9392,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9457,7 +9453,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9472,21 +9468,21 @@
         <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>440</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9509,19 +9505,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9570,7 +9566,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9585,21 +9581,21 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9705,10 +9701,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9816,10 +9812,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9845,16 +9841,16 @@
         <v>160</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9867,7 +9863,7 @@
         <v>20</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>20</v>
@@ -9882,28 +9878,28 @@
         <v>213</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9924,15 +9920,15 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9958,13 +9954,13 @@
         <v>160</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9978,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>20</v>
@@ -9993,28 +9989,28 @@
         <v>213</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -10035,15 +10031,15 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10069,13 +10065,13 @@
         <v>98</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>284</v>
@@ -10091,43 +10087,43 @@
         <v>20</v>
       </c>
       <c r="T71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -10148,15 +10144,15 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10182,10 +10178,10 @@
         <v>98</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10200,43 +10196,43 @@
         <v>20</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10251,25 +10247,25 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10291,10 +10287,10 @@
         <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10309,43 +10305,43 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10360,25 +10356,25 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10400,13 +10396,13 @@
         <v>98</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10420,43 +10416,43 @@
         <v>20</v>
       </c>
       <c r="T74" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10471,25 +10467,25 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10511,10 +10507,10 @@
         <v>98</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10565,7 +10561,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10580,25 +10576,25 @@
         <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10620,10 +10616,10 @@
         <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10638,43 +10634,43 @@
         <v>20</v>
       </c>
       <c r="T76" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10689,21 +10685,21 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10729,13 +10725,13 @@
         <v>98</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10785,7 +10781,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10800,21 +10796,21 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10840,14 +10836,14 @@
         <v>246</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10860,43 +10856,43 @@
         <v>20</v>
       </c>
       <c r="T78" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10911,21 +10907,21 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10948,13 +10944,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11005,7 +11001,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -11020,21 +11016,21 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11060,14 +11056,14 @@
         <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11116,7 +11112,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -11131,7 +11127,7 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -11142,10 +11138,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11251,10 +11247,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11362,10 +11358,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11391,13 +11387,13 @@
         <v>98</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11447,16 +11443,16 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>96</v>
@@ -11473,10 +11469,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11502,13 +11498,13 @@
         <v>126</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11537,28 +11533,28 @@
         <v>142</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11584,10 +11580,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11613,13 +11609,13 @@
         <v>199</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11669,7 +11665,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11684,7 +11680,7 @@
         <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
@@ -11695,10 +11691,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11804,10 +11800,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11915,10 +11911,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12028,10 +12024,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12141,10 +12137,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12254,10 +12250,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12365,10 +12361,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12474,10 +12470,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12585,10 +12581,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12614,13 +12610,13 @@
         <v>98</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12670,7 +12666,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12696,10 +12692,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12722,17 +12718,17 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -12781,7 +12777,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12796,10 +12792,10 @@
         <v>96</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -12807,10 +12803,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12833,13 +12829,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12890,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12905,7 +12901,7 @@
         <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>
@@ -12916,10 +12912,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13025,10 +13021,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13136,14 +13132,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13165,10 +13161,10 @@
         <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>108</v>
@@ -13223,7 +13219,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -13249,10 +13245,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13275,13 +13271,13 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13332,7 +13328,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>84</v>
@@ -13347,7 +13343,7 @@
         <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>20</v>
@@ -13358,10 +13354,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13467,10 +13463,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13578,10 +13574,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13607,13 +13603,13 @@
         <v>98</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13663,16 +13659,16 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>96</v>
@@ -13689,10 +13685,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13718,13 +13714,13 @@
         <v>126</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13753,28 +13749,28 @@
         <v>142</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13800,10 +13796,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13829,13 +13825,13 @@
         <v>199</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13885,7 +13881,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -13900,7 +13896,7 @@
         <v>96</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>20</v>
@@ -13911,10 +13907,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13940,13 +13936,13 @@
         <v>98</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13996,7 +13992,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14022,10 +14018,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14051,10 +14047,10 @@
         <v>160</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14084,11 +14080,11 @@
         <v>213</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
       </c>
@@ -14105,7 +14101,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14120,7 +14116,7 @@
         <v>96</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>20</v>

--- a/main/StructureDefinition-Person.xlsx
+++ b/main/StructureDefinition-Person.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025.2.0</t>
+    <t>2026.1.0</t>
   </si>
   <si>
     <t>Name</t>
